--- a/history_prices/APR/prices_09042026.xlsx
+++ b/history_prices/APR/prices_09042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\APR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F90AB1-F93C-40DE-964D-927C5B44E0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40970431-9C55-415B-9D14-3C490094B9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,9 +690,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.000_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.00_-"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.000_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.00_-"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -725,9 +725,9 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1036,7 +1036,7 @@
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="44.85546875" customWidth="1"/>
     <col min="4" max="5" width="26.42578125" customWidth="1"/>
     <col min="6" max="6" width="23.28515625" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
@@ -3829,7 +3829,7 @@
         <v>14</v>
       </c>
       <c r="E81" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F81" s="2">
         <v>1.714</v>
@@ -3858,7 +3858,7 @@
         <v>19</v>
       </c>
       <c r="E82" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F82" s="2">
         <v>1.399</v>

--- a/history_prices/APR/prices_09042026.xlsx
+++ b/history_prices/APR/prices_09042026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\APR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40970431-9C55-415B-9D14-3C490094B9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4B4442-03F1-4F72-A0D0-5055D7B9593F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ЕКО БЮЛЕТИН" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -703,12 +703,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -723,12 +729,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1372,79 +1383,80 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:13" s="5" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="1">
-        <v>46121</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="6">
+        <v>46121</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1.714</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1.714</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H10" s="9">
+        <f>F10+G10</f>
+        <v>1.744</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="5" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46121</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1.714</v>
+      </c>
+      <c r="G11" s="8">
         <v>0.02</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H11" s="9">
         <v>1.734</v>
       </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="1">
-        <v>46121</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1.714</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1.734</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="I11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="5" t="s">
         <v>45</v>
       </c>
     </row>

--- a/history_prices/APR/prices_09042026.xlsx
+++ b/history_prices/APR/prices_09042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\APR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4B4442-03F1-4F72-A0D0-5055D7B9593F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E89742-B0C8-4909-9F73-FDB2BB6EF7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
